--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N67_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N67_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.23092506898092</v>
+        <v>6.7000253237094</v>
       </c>
       <c r="D2" t="n">
-        <v>35.63772868920204</v>
+        <v>5.791130911995331</v>
       </c>
       <c r="E2" t="n">
-        <v>11.60567418389594</v>
+        <v>1.88592205488309</v>
       </c>
       <c r="F2" t="n">
-        <v>9.411511411566911</v>
+        <v>1.529370604379623</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.08155694142967</v>
+        <v>7.650753002982321</v>
       </c>
       <c r="D3" t="n">
-        <v>42.09177350573236</v>
+        <v>6.839913194681508</v>
       </c>
       <c r="E3" t="n">
-        <v>11.60567418389594</v>
+        <v>1.88592205488309</v>
       </c>
       <c r="F3" t="n">
-        <v>9.411511411566911</v>
+        <v>1.529370604379623</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.61401309301225</v>
+        <v>2.699777127614491</v>
       </c>
       <c r="D4" t="n">
-        <v>18.86794546664065</v>
+        <v>3.066041138329105</v>
       </c>
       <c r="E4" t="n">
-        <v>11.60567418389594</v>
+        <v>1.88592205488309</v>
       </c>
       <c r="F4" t="n">
-        <v>9.411511411566911</v>
+        <v>1.529370604379623</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.05725881194304</v>
+        <v>3.259304556940744</v>
       </c>
       <c r="D5" t="n">
-        <v>21.31833609763657</v>
+        <v>3.464229615865942</v>
       </c>
       <c r="E5" t="n">
-        <v>11.60567418389594</v>
+        <v>1.88592205488309</v>
       </c>
       <c r="F5" t="n">
-        <v>9.411511411566911</v>
+        <v>1.529370604379623</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.6521684513749</v>
+        <v>4.005977373348421</v>
       </c>
       <c r="D6" t="n">
-        <v>26.81215108368061</v>
+        <v>4.3569745510981</v>
       </c>
       <c r="E6" t="n">
-        <v>11.60567418389594</v>
+        <v>1.88592205488309</v>
       </c>
       <c r="F6" t="n">
-        <v>9.411511411566911</v>
+        <v>1.529370604379623</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.94444365259655</v>
+        <v>6.49097209354694</v>
       </c>
       <c r="D7" t="n">
-        <v>42.34261372485247</v>
+        <v>6.880674730288526</v>
       </c>
       <c r="E7" t="n">
-        <v>11.60567418389594</v>
+        <v>1.88592205488309</v>
       </c>
       <c r="F7" t="n">
-        <v>9.411511411566911</v>
+        <v>1.529370604379623</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
